--- a/artfynd/A 33874-2021 artfynd.xlsx
+++ b/artfynd/A 33874-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33874-2021 artfynd.xlsx
+++ b/artfynd/A 33874-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91131154</v>
+        <v>91131142</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438819.0415152195</v>
+        <v>438674</v>
       </c>
       <c r="R2" t="n">
-        <v>7041728.094583577</v>
+        <v>7041798</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91131160</v>
+        <v>91131148</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Halbodarna_NV, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438583.0195240111</v>
+        <v>438683</v>
       </c>
       <c r="R3" t="n">
-        <v>7041922.94272385</v>
+        <v>7041846</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,21 +849,11 @@
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +862,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91131145</v>
+        <v>91131154</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438683.0797622144</v>
+        <v>438819</v>
       </c>
       <c r="R4" t="n">
-        <v>7041845.96605233</v>
+        <v>7041728</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +955,9 @@
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91131148</v>
+        <v>91131159</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,14 +1024,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Halbodarna_NV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438683.0797622144</v>
+        <v>438583</v>
       </c>
       <c r="R5" t="n">
-        <v>7041845.96605233</v>
+        <v>7041923</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,21 +1061,11 @@
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,11 +1074,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1154,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91131159</v>
+        <v>91131145</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,34 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halbodarna_NV, Jmt</t>
+          <t>Halbodarna_SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438583.0195240111</v>
+        <v>438683</v>
       </c>
       <c r="R6" t="n">
-        <v>7041922.94272385</v>
+        <v>7041846</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,21 +1162,11 @@
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1250,6 +1175,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1263,6 +1193,213 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91131160</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Halbodarna_NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>438583</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7041923</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91131141</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>438674</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7041798</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
